--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86205E03-71D1-44CD-AC25-3FDAD4692CB5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CD20D02-24D4-4931-A43F-372376CD2C18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -111,17 +111,17 @@
     <t>USA</t>
   </si>
   <si>
-    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
-  </si>
-  <si>
     <t>ContactTypeInternal__c</t>
+  </si>
+  <si>
+    <t>Southside Community Criminal Justice Board</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +140,13 @@
     <font>
       <sz val="7"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -165,13 +172,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -547,8 +557,8 @@
       <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" t="s">
-        <v>26</v>
+      <c r="C5" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -673,7 +683,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>13</v>

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C4211-89A9-4D8A-9F12-90084029D348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F349C6-DA2C-48C5-A0E2-30B3959D5F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -87,35 +87,35 @@
     <t>AutomationManager@yopmail.com</t>
   </si>
   <si>
-    <t>fieldAccountId</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
-    <t>fieldMailingStreet</t>
-  </si>
-  <si>
-    <t>fieldMailingCity</t>
-  </si>
-  <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
     <t>VA</t>
   </si>
   <si>
-    <t>fieldMailingPostalCode</t>
-  </si>
-  <si>
-    <t>fieldMailingCountry</t>
+    <t>MailingStreet</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
+  </si>
+  <si>
+    <t>AccountId</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -133,12 +133,6 @@
     </font>
     <font>
       <sz val="7"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="5"/>
       <color rgb="FF222222"/>
       <name val="Consolas"/>
       <family val="3"/>
@@ -165,14 +159,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -192,9 +185,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +225,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +331,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +473,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -489,15 +482,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D21291-1546-4312-AD3E-AC2481560893}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -508,18 +501,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -530,7 +523,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -541,7 +534,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -552,7 +545,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -563,7 +556,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -574,7 +567,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -585,7 +578,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -596,7 +589,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -604,26 +597,26 @@
         <v>22</v>
       </c>
       <c r="C10" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11">
         <v>20171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
@@ -641,13 +634,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321AD5C1-CFBB-4EF4-9C99-C433DBDD2201}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -669,7 +662,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
     </row>
   </sheetData>

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08C4211-89A9-4D8A-9F12-90084029D348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1802530A-43D4-48E3-B001-C58678A0EF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -87,28 +87,28 @@
     <t>AutomationManager@yopmail.com</t>
   </si>
   <si>
-    <t>fieldAccountId</t>
-  </si>
-  <si>
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
-    <t>fieldMailingStreet</t>
-  </si>
-  <si>
-    <t>fieldMailingCity</t>
-  </si>
-  <si>
-    <t>fieldState__c</t>
-  </si>
-  <si>
     <t>VA</t>
   </si>
   <si>
-    <t>fieldMailingPostalCode</t>
-  </si>
-  <si>
-    <t>fieldMailingCountry</t>
+    <t>AccountId</t>
+  </si>
+  <si>
+    <t>MailingStreet</t>
+  </si>
+  <si>
+    <t>MailingCity</t>
+  </si>
+  <si>
+    <t>State__c</t>
+  </si>
+  <si>
+    <t>MailingPostalCode</t>
+  </si>
+  <si>
+    <t>MailingCountry</t>
   </si>
 </sst>
 </file>
@@ -192,9 +192,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -232,7 +232,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -338,7 +338,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -480,7 +480,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -513,10 +513,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -579,7 +579,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
@@ -590,7 +590,7 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>13</v>
@@ -601,10 +601,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1802530A-43D4-48E3-B001-C58678A0EF11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A58B2-1904-4442-9409-6A3EC8FCD52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>Ms.</t>
-  </si>
-  <si>
-    <t>704-777-(7868)</t>
   </si>
   <si>
     <t>SterlingUSA</t>
@@ -513,10 +510,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -527,7 +524,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -538,7 +535,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -549,7 +546,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -559,8 +556,8 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
+      <c r="C6" s="2">
+        <v>7047777868</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -579,10 +576,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -590,10 +587,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -601,10 +598,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -612,7 +609,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C11">
         <v>20171</v>
@@ -623,10 +620,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New Project\ProdLWC_Mine\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC1A58B2-1904-4442-9409-6A3EC8FCD52D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{200ADA46-3FBF-4E75-B0FA-4CF7644666A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
@@ -112,7 +112,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -140,6 +140,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1A1B21"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -162,7 +168,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -170,6 +176,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -553,7 +560,7 @@
       <c r="A6" t="s">
         <v>3</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C6" s="2">

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8F349C6-DA2C-48C5-A0E2-30B3959D5F02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990DA1E9-5982-40EA-9490-472A6943A6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="25">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -69,9 +69,6 @@
     <t>Ms.</t>
   </si>
   <si>
-    <t>704-777-(7868)</t>
-  </si>
-  <si>
     <t>SterlingUSA</t>
   </si>
   <si>
@@ -90,9 +87,6 @@
     <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
   </si>
   <si>
-    <t>VA</t>
-  </si>
-  <si>
     <t>MailingStreet</t>
   </si>
   <si>
@@ -109,6 +103,9 @@
   </si>
   <si>
     <t>AccountId</t>
+  </si>
+  <si>
+    <t>AK</t>
   </si>
 </sst>
 </file>
@@ -506,10 +503,10 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -520,7 +517,7 @@
         <v>6</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -531,7 +528,7 @@
         <v>5</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -542,7 +539,7 @@
         <v>4</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -552,8 +549,8 @@
       <c r="B6" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>12</v>
+      <c r="C6" s="2">
+        <v>7856789209</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -572,10 +569,10 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -583,10 +580,10 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -594,10 +591,10 @@
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -605,7 +602,7 @@
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C11">
         <v>20171</v>
@@ -616,10 +613,10 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{990DA1E9-5982-40EA-9490-472A6943A6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9965F437-5CB9-4C28-866A-101B98666C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
@@ -105,7 +105,7 @@
     <t>AccountId</t>
   </si>
   <si>
-    <t>AK</t>
+    <t>AK: Alaska</t>
   </si>
 </sst>
 </file>

--- a/src/main/resources/SubrecipientContact_Field_Values.xlsx
+++ b/src/main/resources/SubrecipientContact_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9965F437-5CB9-4C28-866A-101B98666C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98D5820-C8A5-489F-8B5F-B6F34038057A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9C2C5CEA-7821-409A-A434-0BC7CE36CBA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -84,9 +84,6 @@
     <t>AutomationManager@yopmail.com</t>
   </si>
   <si>
-    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
-  </si>
-  <si>
     <t>MailingStreet</t>
   </si>
   <si>
@@ -106,6 +103,9 @@
   </si>
   <si>
     <t>AK: Alaska</t>
+  </si>
+  <si>
+    <t>205 Legal Services</t>
   </si>
 </sst>
 </file>
@@ -479,15 +479,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D21291-1546-4312-AD3E-AC2481560893}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.44140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -498,18 +498,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -520,7 +520,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -531,7 +531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -542,7 +542,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -553,7 +553,7 @@
         <v>7856789209</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -564,56 +564,56 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B11" t="s">
         <v>20</v>
-      </c>
-      <c r="C10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>3</v>
-      </c>
-      <c r="B11" t="s">
-        <v>21</v>
       </c>
       <c r="C11">
         <v>20171</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
         <v>13</v>
@@ -631,13 +631,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{321AD5C1-CFBB-4EF4-9C99-C433DBDD2201}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -648,7 +648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -659,7 +659,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
     </row>
   </sheetData>
